--- a/data/gravel/Sonder Broken Road Ti 2025.xlsx
+++ b/data/gravel/Sonder Broken Road Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876A0568-9CD4-D94C-A8B2-0DE0FD51902C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0EB794-1455-5147-8F39-40AF5DEEF3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="1960" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -1678,8 +1678,8 @@
       <c r="A45" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>72</v>
+      <c r="B45" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">

--- a/data/gravel/Sonder Broken Road Ti 2025.xlsx
+++ b/data/gravel/Sonder Broken Road Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0EB794-1455-5147-8F39-40AF5DEEF3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AC2B6C-058B-D04D-86AA-267694A210F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="1960" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://us.alpkit.com/cdn/shop/files/broken-road-nx_9a4e950d-41cf-4cf3-9a13-77cefce2ef7b.jpg?v=1717522013&amp;width=768</t>
   </si>
 </sst>
 </file>
@@ -804,6 +807,11 @@
         <v>94</v>
       </c>
     </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Sonder Broken Road Ti 2025.xlsx
+++ b/data/gravel/Sonder Broken Road Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AC2B6C-058B-D04D-86AA-267694A210F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DFB4F6-8D9B-FA46-B8AA-EACC068E70D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="1960" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,15 @@
   </si>
   <si>
     <t>https://us.alpkit.com/cdn/shop/files/broken-road-nx_9a4e950d-41cf-4cf3-9a13-77cefce2ef7b.jpg?v=1717522013&amp;width=768</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Sheffield, South Yorkshire, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -758,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1871,6 +1880,17 @@
       <c r="A73" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="B73" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Sonder Broken Road Ti 2025.xlsx
+++ b/data/gravel/Sonder Broken Road Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DFB4F6-8D9B-FA46-B8AA-EACC068E70D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B3776D-4135-2947-8E1D-4FD53F113589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="1960" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,24 @@
   </si>
   <si>
     <t>Sheffield, South Yorkshire, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -767,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U74"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1727,168 +1745,198 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1">
-        <v>31.6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="1">
-        <v>36</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B58" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B70" s="1">
-        <v>2349</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1">
-        <v>3049</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>110</v>
       </c>
     </row>

--- a/data/gravel/Sonder Broken Road Ti 2025.xlsx
+++ b/data/gravel/Sonder Broken Road Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B3776D-4135-2947-8E1D-4FD53F113589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EBCF94-234B-1543-BED2-F0FF3119622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="1960" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -254,12 +254,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>front_center</t>
-  </si>
-  <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>Small</t>
   </si>
   <si>
@@ -384,6 +378,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>Reba RL</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
@@ -799,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
@@ -807,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -831,12 +834,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -844,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -856,19 +859,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="11"/>
@@ -891,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" s="12">
         <v>410</v>
@@ -924,7 +927,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" s="12">
         <v>589</v>
@@ -954,10 +957,10 @@
     </row>
     <row r="11" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" s="12">
         <v>556</v>
@@ -990,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="12">
         <v>105</v>
@@ -1023,7 +1026,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" s="12">
         <v>67</v>
@@ -1056,7 +1059,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14" s="12">
         <v>73</v>
@@ -1089,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" s="1">
         <f>VALUE(LEFT(G15,3))</f>
@@ -1108,16 +1111,16 @@
         <v>440</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
@@ -1134,7 +1137,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" s="12">
         <v>60</v>
@@ -1149,7 +1152,7 @@
         <v>60</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -1169,7 +1172,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C17" s="1">
         <f>VALUE(LEFT(G17,2))</f>
@@ -1188,16 +1191,16 @@
         <v>44</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
@@ -1215,7 +1218,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C18" s="12">
         <v>1117</v>
@@ -1245,7 +1248,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C19" s="12">
         <v>735</v>
@@ -1278,7 +1281,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C20" s="12">
         <v>410</v>
@@ -1311,7 +1314,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C21" s="12">
         <v>585</v>
@@ -1344,11 +1347,21 @@
         <v>12</v>
       </c>
       <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="7"/>
+      <c r="C22" s="12">
+        <v>506</v>
+      </c>
+      <c r="D22" s="12">
+        <v>506</v>
+      </c>
+      <c r="E22" s="12">
+        <v>506</v>
+      </c>
+      <c r="F22" s="12">
+        <v>506</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -1364,13 +1377,21 @@
     </row>
     <row r="23" spans="1:20" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="C23" s="7">
+        <v>100</v>
+      </c>
+      <c r="D23" s="7">
+        <v>100</v>
+      </c>
+      <c r="E23" s="7">
+        <v>100</v>
+      </c>
+      <c r="F23" s="7">
+        <v>100</v>
+      </c>
       <c r="G23" s="7"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
@@ -1381,7 +1402,7 @@
     </row>
     <row r="24" spans="1:20" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="7"/>
@@ -1652,7 +1673,7 @@
         <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1660,7 +1681,7 @@
         <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1668,7 +1689,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1745,32 +1766,32 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1778,7 +1799,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1799,7 +1820,7 @@
         <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1835,7 +1856,7 @@
         <v>53</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1843,7 +1864,7 @@
         <v>54</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1929,15 +1950,15 @@
         <v>67</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
